--- a/reports/test1_summary.xlsx
+++ b/reports/test1_summary.xlsx
@@ -277,11 +277,14 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E21</f>
+              <f>'Table 1'!E22</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -295,12 +298,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$22:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -309,11 +312,14 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E22</f>
+              <f>'Table 1'!E23</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -327,12 +333,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$22:$I$22</f>
+              <f>'Table 1'!$F$23:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -341,11 +347,14 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E23</f>
+              <f>'Table 1'!E24</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -359,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$23:$I$23</f>
+              <f>'Table 1'!$F$24:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -373,11 +382,14 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E24</f>
+              <f>'Table 1'!E25</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -391,12 +403,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$24:$I$24</f>
+              <f>'Table 1'!$F$25:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -405,11 +417,14 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E25</f>
+              <f>'Table 1'!E26</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -423,12 +438,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$25:$I$25</f>
+              <f>'Table 1'!$F$26:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -437,11 +452,14 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E26</f>
+              <f>'Table 1'!E27</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -455,12 +473,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$26:$I$26</f>
+              <f>'Table 1'!$F$27:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -469,11 +487,14 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E27</f>
+              <f>'Table 1'!E28</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -487,12 +508,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$27:$I$27</f>
+              <f>'Table 1'!$F$28:$G$28</f>
             </numRef>
           </val>
         </ser>
@@ -501,11 +522,14 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E28</f>
+              <f>'Table 1'!E29</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -519,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$28:$I$28</f>
+              <f>'Table 1'!$F$29:$G$29</f>
             </numRef>
           </val>
         </ser>
@@ -533,11 +557,14 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E29</f>
+              <f>'Table 1'!E30</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -551,12 +578,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$29:$I$29</f>
+              <f>'Table 1'!$F$30:$G$30</f>
             </numRef>
           </val>
         </ser>
@@ -565,11 +592,14 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E30</f>
+              <f>'Table 1'!E31</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="B65708"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -583,12 +613,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$30:$I$30</f>
+              <f>'Table 1'!$F$31:$G$31</f>
             </numRef>
           </val>
         </ser>
@@ -597,11 +627,14 @@
           <order val="10"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E31</f>
+              <f>'Table 1'!E32</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4F81BD"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -615,12 +648,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$31:$I$31</f>
+              <f>'Table 1'!$F$32:$G$32</f>
             </numRef>
           </val>
         </ser>
@@ -629,11 +662,14 @@
           <order val="11"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E32</f>
+              <f>'Table 1'!E33</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="5F497A"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -647,12 +683,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$32:$I$32</f>
+              <f>'Table 1'!$F$33:$G$33</f>
             </numRef>
           </val>
         </ser>
@@ -661,11 +697,14 @@
           <order val="12"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E33</f>
+              <f>'Table 1'!E34</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -679,12 +718,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$33:$I$33</f>
+              <f>'Table 1'!$F$34:$G$34</f>
             </numRef>
           </val>
         </ser>
@@ -693,11 +732,14 @@
           <order val="13"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E34</f>
+              <f>'Table 1'!E35</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -711,12 +753,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$34:$I$34</f>
+              <f>'Table 1'!$F$35:$G$35</f>
             </numRef>
           </val>
         </ser>
@@ -725,11 +767,14 @@
           <order val="14"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E35</f>
+              <f>'Table 1'!E36</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -743,12 +788,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$35:$I$35</f>
+              <f>'Table 1'!$F$36:$G$36</f>
             </numRef>
           </val>
         </ser>
@@ -757,11 +802,14 @@
           <order val="15"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E36</f>
+              <f>'Table 1'!E37</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -775,44 +823,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$36:$I$36</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="16"/>
-          <order val="16"/>
-          <tx>
-            <strRef>
-              <f>'Table 1'!E37</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Table 1'!$F$37:$I$37</f>
+              <f>'Table 1'!$F$37:$G$37</f>
             </numRef>
           </val>
         </ser>
@@ -1197,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1208,7 +1224,6 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1501,12 +1516,6 @@
         <v>3</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1537,14 +1546,6 @@
         <v/>
       </c>
       <c r="G22" s="15">
-        <f>C22-D22*4</f>
-        <v/>
-      </c>
-      <c r="H22" s="15">
-        <f>C22-D22*5</f>
-        <v/>
-      </c>
-      <c r="I22" s="15">
         <f>C22-D22*6</f>
         <v/>
       </c>
@@ -1576,14 +1577,6 @@
         <v/>
       </c>
       <c r="G23" s="15">
-        <f>C23-D23*4</f>
-        <v/>
-      </c>
-      <c r="H23" s="15">
-        <f>C23-D23*5</f>
-        <v/>
-      </c>
-      <c r="I23" s="15">
         <f>C23-D23*6</f>
         <v/>
       </c>
@@ -1615,14 +1608,6 @@
         <v/>
       </c>
       <c r="G24" s="15">
-        <f>C24-D24*4</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>C24-D24*5</f>
-        <v/>
-      </c>
-      <c r="I24" s="15">
         <f>C24-D24*6</f>
         <v/>
       </c>
@@ -1654,14 +1639,6 @@
         <v/>
       </c>
       <c r="G25" s="15">
-        <f>C25-D25*4</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>C25-D25*5</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
         <f>C25-D25*6</f>
         <v/>
       </c>
@@ -1693,14 +1670,6 @@
         <v/>
       </c>
       <c r="G26" s="15">
-        <f>C26-D26*4</f>
-        <v/>
-      </c>
-      <c r="H26" s="15">
-        <f>C26-D26*5</f>
-        <v/>
-      </c>
-      <c r="I26" s="15">
         <f>C26-D26*6</f>
         <v/>
       </c>
@@ -1732,14 +1701,6 @@
         <v/>
       </c>
       <c r="G27" s="15">
-        <f>C27-D27*4</f>
-        <v/>
-      </c>
-      <c r="H27" s="15">
-        <f>C27-D27*5</f>
-        <v/>
-      </c>
-      <c r="I27" s="15">
         <f>C27-D27*6</f>
         <v/>
       </c>
@@ -1771,14 +1732,6 @@
         <v/>
       </c>
       <c r="G28" s="15">
-        <f>C28-D28*4</f>
-        <v/>
-      </c>
-      <c r="H28" s="15">
-        <f>C28-D28*5</f>
-        <v/>
-      </c>
-      <c r="I28" s="15">
         <f>C28-D28*6</f>
         <v/>
       </c>
@@ -1810,14 +1763,6 @@
         <v/>
       </c>
       <c r="G29" s="15">
-        <f>C29-D29*4</f>
-        <v/>
-      </c>
-      <c r="H29" s="15">
-        <f>C29-D29*5</f>
-        <v/>
-      </c>
-      <c r="I29" s="15">
         <f>C29-D29*6</f>
         <v/>
       </c>
@@ -1849,14 +1794,6 @@
         <v/>
       </c>
       <c r="G30" s="15">
-        <f>C30-D30*4</f>
-        <v/>
-      </c>
-      <c r="H30" s="15">
-        <f>C30-D30*5</f>
-        <v/>
-      </c>
-      <c r="I30" s="15">
         <f>C30-D30*6</f>
         <v/>
       </c>
@@ -1888,14 +1825,6 @@
         <v/>
       </c>
       <c r="G31" s="15">
-        <f>C31-D31*4</f>
-        <v/>
-      </c>
-      <c r="H31" s="15">
-        <f>C31-D31*5</f>
-        <v/>
-      </c>
-      <c r="I31" s="15">
         <f>C31-D31*6</f>
         <v/>
       </c>
@@ -1927,14 +1856,6 @@
         <v/>
       </c>
       <c r="G32" s="15">
-        <f>C32-D32*4</f>
-        <v/>
-      </c>
-      <c r="H32" s="15">
-        <f>C32-D32*5</f>
-        <v/>
-      </c>
-      <c r="I32" s="15">
         <f>C32-D32*6</f>
         <v/>
       </c>
@@ -1966,14 +1887,6 @@
         <v/>
       </c>
       <c r="G33" s="15">
-        <f>C33-D33*4</f>
-        <v/>
-      </c>
-      <c r="H33" s="15">
-        <f>C33-D33*5</f>
-        <v/>
-      </c>
-      <c r="I33" s="15">
         <f>C33-D33*6</f>
         <v/>
       </c>
@@ -2005,14 +1918,6 @@
         <v/>
       </c>
       <c r="G34" s="15">
-        <f>C34-D34*4</f>
-        <v/>
-      </c>
-      <c r="H34" s="15">
-        <f>C34-D34*5</f>
-        <v/>
-      </c>
-      <c r="I34" s="15">
         <f>C34-D34*6</f>
         <v/>
       </c>
@@ -2044,14 +1949,6 @@
         <v/>
       </c>
       <c r="G35" s="15">
-        <f>C35-D35*4</f>
-        <v/>
-      </c>
-      <c r="H35" s="15">
-        <f>C35-D35*5</f>
-        <v/>
-      </c>
-      <c r="I35" s="15">
         <f>C35-D35*6</f>
         <v/>
       </c>
@@ -2083,14 +1980,6 @@
         <v/>
       </c>
       <c r="G36" s="15">
-        <f>C36-D36*4</f>
-        <v/>
-      </c>
-      <c r="H36" s="15">
-        <f>C36-D36*5</f>
-        <v/>
-      </c>
-      <c r="I36" s="15">
         <f>C36-D36*6</f>
         <v/>
       </c>
@@ -2122,14 +2011,6 @@
         <v/>
       </c>
       <c r="G37" s="15">
-        <f>C37-D37*4</f>
-        <v/>
-      </c>
-      <c r="H37" s="15">
-        <f>C37-D37*5</f>
-        <v/>
-      </c>
-      <c r="I37" s="15">
         <f>C37-D37*6</f>
         <v/>
       </c>

--- a/reports/test1_summary.xlsx
+++ b/reports/test1_summary.xlsx
@@ -840,6 +840,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -858,6 +859,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -865,7 +867,10 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="-8.539999999999999"/>
+          <min val="-11.67"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -885,6 +890,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -1213,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2020,7 +2026,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXTRACTED TABLE DATA</t>
+          <t>EXTRACTED RAW TABLE DATA</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -2068,543 +2074,431 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>THF-d8</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.519361</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>2.20882</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr"/>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>CDCl 3</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>0.74596</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.534677</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>2.34303</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr"/>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>C 6 D 6</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>0.72682</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>1.91203</v>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>0.6067</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>toluene- d 8</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>0.73512</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.531065</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>2.13758</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr"/>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>CD 2 Cl 2</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>0.01155</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>0.70628</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.5214530000000001</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>2.74368</v>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>0.413</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr"/>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>acetone- d 6</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>0.07135</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>0.49819</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.452089</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>2.0934</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>PEO</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>CD 3 OD</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>0.03563</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>0.65424</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0.504105</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>1.43345</v>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
     <row r="49">
       <c r="A49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr"/>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>THF-d8</t>
+          <t>D 2 O</t>
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>0.0141</v>
+        <v>0.02554</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>0.7</v>
+        <v>0.67839</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.519361</v>
+        <v>0.512155</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>2.20882</v>
+        <v>0.792177</v>
       </c>
       <c r="H49" s="13" t="n">
+        <v>1.098</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr"/>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>THF- d 8</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.513725</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>1.8457</v>
+      </c>
+      <c r="H50" s="13" t="n">
         <v>0.48</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
+    <row r="51">
+      <c r="A51" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr"/>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>CD 3 CN</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>0.02456</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>0.68948</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0.515853</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>2.56919</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0.343</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr"/>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>acetone- d 6</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="n">
+        <v>0.06862</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>0.56535</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.474477</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>2.12079</v>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>PMMA</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>THF- d 8</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>0.69474</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0.517608</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>2.42854</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr"/>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>CDCl 3</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>0.00517</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>0.77158</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.543219</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>2.63117</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr"/>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>C 6 D 6</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>0.00848</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>0.7331</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0.530394</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>2.07035</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>0.6067</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr"/>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>CD 2 Cl 2</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>0.75226</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>0.53678</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>3.23833</v>
+      </c>
+      <c r="H56" s="13" t="n">
+        <v>0.413</v>
+      </c>
+    </row>
     <row r="57">
       <c r="A57" s="13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B57" s="12" t="inlineStr"/>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>CDCl 3</t>
+          <t>DMSO</t>
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>0.00732</v>
+        <v>0.05265</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>0.74596</v>
+        <v>0.47463</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.534677</v>
+        <v>0.444236</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>2.34303</v>
+        <v>0.312052</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B65" s="12" t="inlineStr"/>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>C 6 D 6</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="n">
-        <v>0.01077</v>
-      </c>
-      <c r="E65" s="13" t="n">
-        <v>0.72682</v>
-      </c>
-      <c r="F65" s="13" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="G65" s="13" t="n">
-        <v>1.91203</v>
-      </c>
-      <c r="H65" s="13" t="n">
-        <v>0.6067</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" s="12" t="inlineStr"/>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>toluene- d 8</t>
-        </is>
-      </c>
-      <c r="D73" s="13" t="n">
-        <v>0.0098</v>
-      </c>
-      <c r="E73" s="13" t="n">
-        <v>0.73512</v>
-      </c>
-      <c r="F73" s="13" t="n">
-        <v>0.531065</v>
-      </c>
-      <c r="G73" s="13" t="n">
-        <v>2.13758</v>
-      </c>
-      <c r="H73" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B81" s="12" t="inlineStr"/>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>CD 2 Cl 2</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="n">
-        <v>0.01155</v>
-      </c>
-      <c r="E81" s="13" t="n">
-        <v>0.70628</v>
-      </c>
-      <c r="F81" s="13" t="n">
-        <v>0.5214530000000001</v>
-      </c>
-      <c r="G81" s="13" t="n">
-        <v>2.74368</v>
-      </c>
-      <c r="H81" s="13" t="n">
-        <v>0.413</v>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89">
-      <c r="A89" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B89" s="12" t="inlineStr"/>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>acetone- d 6</t>
-        </is>
-      </c>
-      <c r="D89" s="13" t="n">
-        <v>0.07135</v>
-      </c>
-      <c r="E89" s="13" t="n">
-        <v>0.49819</v>
-      </c>
-      <c r="F89" s="13" t="n">
-        <v>0.452089</v>
-      </c>
-      <c r="G89" s="13" t="n">
-        <v>2.0934</v>
-      </c>
-      <c r="H89" s="13" t="n">
-        <v>0.295</v>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97">
-      <c r="A97" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>PEO</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>CD 3 OD</t>
-        </is>
-      </c>
-      <c r="D97" s="13" t="n">
-        <v>0.03563</v>
-      </c>
-      <c r="E97" s="13" t="n">
-        <v>0.65424</v>
-      </c>
-      <c r="F97" s="13" t="n">
-        <v>0.504105</v>
-      </c>
-      <c r="G97" s="13" t="n">
-        <v>1.43345</v>
-      </c>
-      <c r="H97" s="13" t="n">
-        <v>0.543</v>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B105" s="12" t="inlineStr"/>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>D 2 O</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="n">
-        <v>0.02554</v>
-      </c>
-      <c r="E105" s="13" t="n">
-        <v>0.67839</v>
-      </c>
-      <c r="F105" s="13" t="n">
-        <v>0.512155</v>
-      </c>
-      <c r="G105" s="13" t="n">
-        <v>0.792177</v>
-      </c>
-      <c r="H105" s="13" t="n">
-        <v>1.098</v>
-      </c>
-    </row>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113">
-      <c r="A113" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B113" s="12" t="inlineStr"/>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>THF- d 8</t>
-        </is>
-      </c>
-      <c r="D113" s="13" t="n">
-        <v>0.02417</v>
-      </c>
-      <c r="E113" s="13" t="n">
-        <v>0.6831</v>
-      </c>
-      <c r="F113" s="13" t="n">
-        <v>0.513725</v>
-      </c>
-      <c r="G113" s="13" t="n">
-        <v>1.8457</v>
-      </c>
-      <c r="H113" s="13" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121">
-      <c r="A121" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B121" s="12" t="inlineStr"/>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>CD 3 CN</t>
-        </is>
-      </c>
-      <c r="D121" s="13" t="n">
-        <v>0.02456</v>
-      </c>
-      <c r="E121" s="13" t="n">
-        <v>0.68948</v>
-      </c>
-      <c r="F121" s="13" t="n">
-        <v>0.515853</v>
-      </c>
-      <c r="G121" s="13" t="n">
-        <v>2.56919</v>
-      </c>
-      <c r="H121" s="13" t="n">
-        <v>0.343</v>
-      </c>
-    </row>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129">
-      <c r="A129" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B129" s="12" t="inlineStr"/>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>acetone- d 6</t>
-        </is>
-      </c>
-      <c r="D129" s="13" t="n">
-        <v>0.06862</v>
-      </c>
-      <c r="E129" s="13" t="n">
-        <v>0.56535</v>
-      </c>
-      <c r="F129" s="13" t="n">
-        <v>0.474477</v>
-      </c>
-      <c r="G129" s="13" t="n">
-        <v>2.12079</v>
-      </c>
-      <c r="H129" s="13" t="n">
-        <v>0.295</v>
-      </c>
-    </row>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137">
-      <c r="A137" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B137" s="12" t="inlineStr">
-        <is>
-          <t>PMMA</t>
-        </is>
-      </c>
-      <c r="C137" s="12" t="inlineStr">
-        <is>
-          <t>THF- d 8</t>
-        </is>
-      </c>
-      <c r="D137" s="13" t="n">
-        <v>0.01061</v>
-      </c>
-      <c r="E137" s="13" t="n">
-        <v>0.69474</v>
-      </c>
-      <c r="F137" s="13" t="n">
-        <v>0.517608</v>
-      </c>
-      <c r="G137" s="13" t="n">
-        <v>2.42854</v>
-      </c>
-      <c r="H137" s="13" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145">
-      <c r="A145" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B145" s="12" t="inlineStr"/>
-      <c r="C145" s="12" t="inlineStr">
-        <is>
-          <t>CDCl 3</t>
-        </is>
-      </c>
-      <c r="D145" s="13" t="n">
-        <v>0.00517</v>
-      </c>
-      <c r="E145" s="13" t="n">
-        <v>0.77158</v>
-      </c>
-      <c r="F145" s="13" t="n">
-        <v>0.543219</v>
-      </c>
-      <c r="G145" s="13" t="n">
-        <v>2.63117</v>
-      </c>
-      <c r="H145" s="13" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-    </row>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153">
-      <c r="A153" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B153" s="12" t="inlineStr"/>
-      <c r="C153" s="12" t="inlineStr">
-        <is>
-          <t>C 6 D 6</t>
-        </is>
-      </c>
-      <c r="D153" s="13" t="n">
-        <v>0.00848</v>
-      </c>
-      <c r="E153" s="13" t="n">
-        <v>0.7331</v>
-      </c>
-      <c r="F153" s="13" t="n">
-        <v>0.530394</v>
-      </c>
-      <c r="G153" s="13" t="n">
-        <v>2.07035</v>
-      </c>
-      <c r="H153" s="13" t="n">
-        <v>0.6067</v>
-      </c>
-    </row>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161">
-      <c r="A161" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B161" s="12" t="inlineStr"/>
-      <c r="C161" s="12" t="inlineStr">
-        <is>
-          <t>CD 2 Cl 2</t>
-        </is>
-      </c>
-      <c r="D161" s="13" t="n">
-        <v>0.00702</v>
-      </c>
-      <c r="E161" s="13" t="n">
-        <v>0.75226</v>
-      </c>
-      <c r="F161" s="13" t="n">
-        <v>0.53678</v>
-      </c>
-      <c r="G161" s="13" t="n">
-        <v>3.23833</v>
-      </c>
-      <c r="H161" s="13" t="n">
-        <v>0.413</v>
-      </c>
-    </row>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169">
-      <c r="A169" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B169" s="12" t="inlineStr"/>
-      <c r="C169" s="12" t="inlineStr">
-        <is>
-          <t>DMSO</t>
-        </is>
-      </c>
-      <c r="D169" s="13" t="n">
-        <v>0.05265</v>
-      </c>
-      <c r="E169" s="13" t="n">
-        <v>0.47463</v>
-      </c>
-      <c r="F169" s="13" t="n">
-        <v>0.444236</v>
-      </c>
-      <c r="G169" s="13" t="n">
-        <v>0.312052</v>
-      </c>
-      <c r="H169" s="13" t="n">
         <v>2.19</v>
       </c>
     </row>

--- a/reports/test1_summary.xlsx
+++ b/reports/test1_summary.xlsx
@@ -867,8 +867,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="-8.539999999999999"/>
-          <min val="-11.67"/>
+          <max val="-8.94"/>
+          <min val="-11.27"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -912,7 +912,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6480000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
